--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,6 +790,117 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120111342</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, sydost om, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>339179</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6433269</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Torrträd av tall med spillkråkehack vid basen. Naturskogsartad skog.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,6 +901,470 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120252553</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, sydost om, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>339326</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6433296</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spillkråkehack vid basen hos en högstubbe av tall eller gran.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120252502</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96175</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, sydost om, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>339314</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6433300</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120253024</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5169</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, sydost om, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>339324</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6433300</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Noterades på samma relativt klena torrträd av gran som den vågbandade barkbocken.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120252645</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5189</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, sydost om, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>339324</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6433300</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>5-6 mm breda gnagspår i veden samt sneda ingångshål noterades på ett relativt klent torrträd av gran.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1365,6 +1365,485 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120271800</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56282</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100088</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vanlig snok</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Natrix natrix</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mickelsdamm 3, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>339227</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6433304</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ingela Eriksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ingela Eriksson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120271247</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mickelsdamm 3, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>339227</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6433304</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ingela Eriksson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ingela Eriksson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120271353</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mickelsdamm 3, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>339298</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6433301</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ingela Eriksson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ingela Eriksson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120271284</v>
+      </c>
+      <c r="B11" t="n">
+        <v>94681</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mickelsdamm 3, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>339298</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6433301</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ingela Eriksson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ingela Eriksson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>120111342</v>
       </c>
       <c r="B3" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120252553</v>
+        <v>120253024</v>
       </c>
       <c r="B4" t="n">
-        <v>57326</v>
+        <v>5169</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,33 +915,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -951,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>339326</v>
+        <v>339324</v>
       </c>
       <c r="R4" t="n">
-        <v>6433296</v>
+        <v>6433300</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -991,7 +992,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spillkråkehack vid basen hos en högstubbe av tall eller gran.</t>
+          <t>Noterades på samma relativt klena torrträd av gran som den vågbandade barkbocken.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,6 +1001,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1018,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120252502</v>
+        <v>120252645</v>
       </c>
       <c r="B5" t="n">
-        <v>96175</v>
+        <v>5189</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,35 +1036,32 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1070,7 +1069,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>339314</v>
+        <v>339324</v>
       </c>
       <c r="R5" t="n">
         <v>6433300</v>
@@ -1106,6 +1105,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>5-6 mm breda gnagspår i veden samt sneda ingångshål noterades på ett relativt klent torrträd av gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120253024</v>
+        <v>120252553</v>
       </c>
       <c r="B6" t="n">
-        <v>5169</v>
+        <v>57336</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,34 +1149,33 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1182,10 +1185,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>339324</v>
+        <v>339326</v>
       </c>
       <c r="R6" t="n">
-        <v>6433300</v>
+        <v>6433296</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1222,7 +1225,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Noterades på samma relativt klena torrträd av gran som den vågbandade barkbocken.</t>
+          <t>Spillkråkehack vid basen hos en högstubbe av tall eller gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,7 +1234,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1250,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120252645</v>
+        <v>120252502</v>
       </c>
       <c r="B7" t="n">
-        <v>5189</v>
+        <v>96198</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,32 +1268,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1299,7 +1304,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>339324</v>
+        <v>339314</v>
       </c>
       <c r="R7" t="n">
         <v>6433300</v>
@@ -1335,11 +1340,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>5-6 mm breda gnagspår i veden samt sneda ingångshål noterades på ett relativt klent torrträd av gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120271800</v>
+        <v>120271247</v>
       </c>
       <c r="B8" t="n">
-        <v>56282</v>
+        <v>57336</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,20 +1379,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100088</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1400,17 +1400,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1455,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,7 +1469,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1493,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120271247</v>
+        <v>120271284</v>
       </c>
       <c r="B9" t="n">
-        <v>57326</v>
+        <v>94704</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,35 +1499,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1541,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>339227</v>
+        <v>339298</v>
       </c>
       <c r="R9" t="n">
-        <v>6433304</v>
+        <v>6433301</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1595,6 +1585,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1616,7 +1607,7 @@
         <v>120271353</v>
       </c>
       <c r="B10" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1729,10 +1720,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120271284</v>
+        <v>120271800</v>
       </c>
       <c r="B11" t="n">
-        <v>94681</v>
+        <v>56292</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1745,27 +1736,36 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>100088</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>339298</v>
+        <v>339227</v>
       </c>
       <c r="R11" t="n">
-        <v>6433301</v>
+        <v>6433304</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120253024</v>
+        <v>120252645</v>
       </c>
       <c r="B4" t="n">
-        <v>5169</v>
+        <v>5189</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -992,7 +992,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Noterades på samma relativt klena torrträd av gran som den vågbandade barkbocken.</t>
+          <t>5-6 mm breda gnagspår i veden samt sneda ingångshål noterades på ett relativt klent torrträd av gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120252645</v>
+        <v>120252553</v>
       </c>
       <c r="B5" t="n">
-        <v>5189</v>
+        <v>57336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,20 +1032,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1054,12 +1054,11 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1069,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>339324</v>
+        <v>339326</v>
       </c>
       <c r="R5" t="n">
-        <v>6433300</v>
+        <v>6433296</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1109,7 +1108,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>5-6 mm breda gnagspår i veden samt sneda ingångshål noterades på ett relativt klent torrträd av gran.</t>
+          <t>Spillkråkehack vid basen hos en högstubbe av tall eller gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,7 +1117,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1137,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120252553</v>
+        <v>120252502</v>
       </c>
       <c r="B6" t="n">
-        <v>57336</v>
+        <v>96198</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,35 +1147,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1185,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>339326</v>
+        <v>339314</v>
       </c>
       <c r="R6" t="n">
-        <v>6433296</v>
+        <v>6433300</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1223,17 +1225,13 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spillkråkehack vid basen hos en högstubbe av tall eller gran.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1252,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120252502</v>
+        <v>120253024</v>
       </c>
       <c r="B7" t="n">
-        <v>96198</v>
+        <v>5169</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,35 +1266,32 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2569</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1304,7 +1299,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>339314</v>
+        <v>339324</v>
       </c>
       <c r="R7" t="n">
         <v>6433300</v>
@@ -1340,6 +1335,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Noterades på samma relativt klena torrträd av gran som den vågbandade barkbocken.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120271247</v>
+        <v>120271800</v>
       </c>
       <c r="B8" t="n">
-        <v>57336</v>
+        <v>56292</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,20 +1379,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100088</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1400,12 +1400,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1450,7 +1455,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1465,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,6 +1474,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1487,10 +1493,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120271284</v>
+        <v>120271353</v>
       </c>
       <c r="B9" t="n">
-        <v>94704</v>
+        <v>57336</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,31 +1505,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1566,7 +1572,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1576,7 +1582,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,7 +1591,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1604,7 +1609,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120271353</v>
+        <v>120271247</v>
       </c>
       <c r="B10" t="n">
         <v>57336</v>
@@ -1640,7 +1645,11 @@
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1648,10 +1657,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>339298</v>
+        <v>339227</v>
       </c>
       <c r="R10" t="n">
-        <v>6433301</v>
+        <v>6433304</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1683,7 +1692,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1693,7 +1702,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,10 +1729,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120271800</v>
+        <v>120271284</v>
       </c>
       <c r="B11" t="n">
-        <v>56292</v>
+        <v>94704</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,36 +1745,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100088</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>339227</v>
+        <v>339298</v>
       </c>
       <c r="R11" t="n">
-        <v>6433304</v>
+        <v>6433301</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120252645</v>
+        <v>120252553</v>
       </c>
       <c r="B4" t="n">
-        <v>5189</v>
+        <v>57336</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,20 +915,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -937,12 +937,11 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -952,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>339324</v>
+        <v>339326</v>
       </c>
       <c r="R4" t="n">
-        <v>6433300</v>
+        <v>6433296</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -992,7 +991,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>5-6 mm breda gnagspår i veden samt sneda ingångshål noterades på ett relativt klent torrträd av gran.</t>
+          <t>Spillkråkehack vid basen hos en högstubbe av tall eller gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +1000,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1020,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120252553</v>
+        <v>120252502</v>
       </c>
       <c r="B5" t="n">
-        <v>57336</v>
+        <v>96198</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,35 +1030,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1068,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>339326</v>
+        <v>339314</v>
       </c>
       <c r="R5" t="n">
-        <v>6433296</v>
+        <v>6433300</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1106,17 +1108,13 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spillkråkehack vid basen hos en högstubbe av tall eller gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1135,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120252502</v>
+        <v>120252645</v>
       </c>
       <c r="B6" t="n">
-        <v>96198</v>
+        <v>5189</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,35 +1149,32 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1187,7 +1182,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>339314</v>
+        <v>339324</v>
       </c>
       <c r="R6" t="n">
         <v>6433300</v>
@@ -1223,6 +1218,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>5-6 mm breda gnagspår i veden samt sneda ingångshål noterades på ett relativt klent torrträd av gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1367,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120271800</v>
+        <v>120271247</v>
       </c>
       <c r="B8" t="n">
-        <v>56292</v>
+        <v>57336</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,20 +1379,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100088</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1400,17 +1400,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1455,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,19 +1469,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1597,22 +1591,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120271247</v>
+        <v>120271800</v>
       </c>
       <c r="B10" t="n">
-        <v>57336</v>
+        <v>56292</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1621,20 +1615,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100088</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1642,12 +1636,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1692,7 +1691,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1702,7 +1701,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,18 +1710,19 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1834,12 +1834,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120252553</v>
+        <v>120252502</v>
       </c>
       <c r="B4" t="n">
-        <v>57336</v>
+        <v>96198</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,35 +915,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>339326</v>
+        <v>339314</v>
       </c>
       <c r="R4" t="n">
-        <v>6433296</v>
+        <v>6433300</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -989,17 +993,13 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spillkråkehack vid basen hos en högstubbe av tall eller gran.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120252502</v>
+        <v>120253024</v>
       </c>
       <c r="B5" t="n">
-        <v>96198</v>
+        <v>5169</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,35 +1034,32 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1070,7 +1067,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>339314</v>
+        <v>339324</v>
       </c>
       <c r="R5" t="n">
         <v>6433300</v>
@@ -1106,6 +1103,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Noterades på samma relativt klena torrträd av gran som den vågbandade barkbocken.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1250,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120253024</v>
+        <v>120252553</v>
       </c>
       <c r="B7" t="n">
-        <v>5169</v>
+        <v>57336</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,34 +1264,33 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1299,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>339324</v>
+        <v>339326</v>
       </c>
       <c r="R7" t="n">
-        <v>6433300</v>
+        <v>6433296</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1339,7 +1340,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Noterades på samma relativt klena torrträd av gran som den vågbandade barkbocken.</t>
+          <t>Spillkråkehack vid basen hos en högstubbe av tall eller gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,7 +1349,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1367,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120271247</v>
+        <v>120271284</v>
       </c>
       <c r="B8" t="n">
-        <v>57336</v>
+        <v>94704</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,35 +1379,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1415,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>339227</v>
+        <v>339298</v>
       </c>
       <c r="R8" t="n">
-        <v>6433304</v>
+        <v>6433301</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1469,6 +1465,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1487,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120271353</v>
+        <v>120271800</v>
       </c>
       <c r="B9" t="n">
-        <v>57336</v>
+        <v>56292</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,20 +1496,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100088</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1520,10 +1517,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1531,10 +1537,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>339298</v>
+        <v>339227</v>
       </c>
       <c r="R9" t="n">
-        <v>6433301</v>
+        <v>6433304</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1585,6 +1591,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1603,10 +1610,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120271800</v>
+        <v>120271353</v>
       </c>
       <c r="B10" t="n">
-        <v>56292</v>
+        <v>57336</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,20 +1622,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100088</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1636,19 +1643,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1656,10 +1654,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>339227</v>
+        <v>339298</v>
       </c>
       <c r="R10" t="n">
-        <v>6433304</v>
+        <v>6433301</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1710,7 +1708,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1729,10 +1726,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120271284</v>
+        <v>120271247</v>
       </c>
       <c r="B11" t="n">
-        <v>94704</v>
+        <v>57336</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1741,31 +1738,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1773,10 +1774,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>339298</v>
+        <v>339227</v>
       </c>
       <c r="R11" t="n">
-        <v>6433301</v>
+        <v>6433304</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1827,7 +1828,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120252502</v>
+        <v>120252553</v>
       </c>
       <c r="B4" t="n">
-        <v>96198</v>
+        <v>57336</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +915,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>339314</v>
+        <v>339326</v>
       </c>
       <c r="R4" t="n">
-        <v>6433300</v>
+        <v>6433296</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,13 +989,17 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spillkråkehack vid basen hos en högstubbe av tall eller gran.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120253024</v>
+        <v>120252502</v>
       </c>
       <c r="B5" t="n">
-        <v>5169</v>
+        <v>96198</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,32 +1034,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1067,7 +1070,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>339324</v>
+        <v>339314</v>
       </c>
       <c r="R5" t="n">
         <v>6433300</v>
@@ -1103,11 +1106,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Noterades på samma relativt klena torrträd av gran som den vågbandade barkbocken.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120252645</v>
+        <v>120253024</v>
       </c>
       <c r="B6" t="n">
-        <v>5189</v>
+        <v>5169</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1224,7 +1222,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>5-6 mm breda gnagspår i veden samt sneda ingångshål noterades på ett relativt klent torrträd av gran.</t>
+          <t>Noterades på samma relativt klena torrträd av gran som den vågbandade barkbocken.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120252553</v>
+        <v>120252645</v>
       </c>
       <c r="B7" t="n">
-        <v>57336</v>
+        <v>5189</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,20 +1262,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1286,11 +1284,12 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1300,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>339326</v>
+        <v>339324</v>
       </c>
       <c r="R7" t="n">
-        <v>6433296</v>
+        <v>6433300</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1340,7 +1339,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Spillkråkehack vid basen hos en högstubbe av tall eller gran.</t>
+          <t>5-6 mm breda gnagspår i veden samt sneda ingångshål noterades på ett relativt klent torrträd av gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,6 +1348,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1367,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120271284</v>
+        <v>120271247</v>
       </c>
       <c r="B8" t="n">
-        <v>94704</v>
+        <v>57336</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,31 +1379,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1411,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>339298</v>
+        <v>339227</v>
       </c>
       <c r="R8" t="n">
-        <v>6433301</v>
+        <v>6433304</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1465,7 +1469,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1726,10 +1729,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120271247</v>
+        <v>120271284</v>
       </c>
       <c r="B11" t="n">
-        <v>57336</v>
+        <v>94704</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,35 +1741,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1774,10 +1773,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>339227</v>
+        <v>339298</v>
       </c>
       <c r="R11" t="n">
-        <v>6433304</v>
+        <v>6433301</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1828,6 +1827,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1843,6 +1843,875 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120506596</v>
+      </c>
+      <c r="B12" t="n">
+        <v>94704</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>339228</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6433280</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Blåmossa mäter 80 cm, samt 60 cm</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog,  naturskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120506478</v>
+      </c>
+      <c r="B13" t="n">
+        <v>96198</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>339233</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6433302</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikt med tuvor av stor revmossa</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog,  naturskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120506387</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5189</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>339233</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6433302</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog,  naturskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120506864</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57689</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>339229</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6433280</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog,  naturskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120506336</v>
+      </c>
+      <c r="B16" t="n">
+        <v>84228</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3518</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Smal svampklubba</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tolypocladium ophioglossoides</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>339237</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6433281</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På berghäll i äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog,  naturskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120506617</v>
+      </c>
+      <c r="B17" t="n">
+        <v>94704</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>339229</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6433303</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Blåmossa mäter 50 cm</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog, naturskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120506916</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>339264</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6433295</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog, naturskog</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1846,10 +1846,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120506596</v>
+        <v>120506478</v>
       </c>
       <c r="B12" t="n">
-        <v>94704</v>
+        <v>96198</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1862,28 +1862,24 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>2569</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1894,10 +1890,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>339228</v>
+        <v>339233</v>
       </c>
       <c r="R12" t="n">
-        <v>6433280</v>
+        <v>6433302</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1934,7 +1930,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Blåmossa mäter 80 cm, samt 60 cm</t>
+          <t>Rikt med tuvor av stor revmossa</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1972,10 +1968,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120506478</v>
+        <v>120506387</v>
       </c>
       <c r="B13" t="n">
-        <v>96198</v>
+        <v>5189</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1988,27 +1984,32 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2569</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2052,11 +2053,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikt med tuvor av stor revmossa</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2094,10 +2090,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120506387</v>
+        <v>120506864</v>
       </c>
       <c r="B14" t="n">
-        <v>5189</v>
+        <v>57689</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2110,16 +2106,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2127,13 +2123,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2143,10 +2142,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>339233</v>
+        <v>339229</v>
       </c>
       <c r="R14" t="n">
-        <v>6433302</v>
+        <v>6433280</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2187,7 +2186,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2216,10 +2214,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120506864</v>
+        <v>120506336</v>
       </c>
       <c r="B15" t="n">
-        <v>57689</v>
+        <v>84228</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2232,35 +2230,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>3518</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2268,10 +2261,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>339229</v>
+        <v>339237</v>
       </c>
       <c r="R15" t="n">
-        <v>6433280</v>
+        <v>6433281</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2306,12 +2299,18 @@
           <t>2024-10-19</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På berghäll i äldre barrblandskog</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2340,10 +2339,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120506336</v>
+        <v>120506916</v>
       </c>
       <c r="B16" t="n">
-        <v>84228</v>
+        <v>57336</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2352,34 +2351,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3518</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2387,13 +2391,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>339237</v>
+        <v>339264</v>
       </c>
       <c r="R16" t="n">
-        <v>6433281</v>
+        <v>6433295</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2425,18 +2429,12 @@
           <t>2024-10-19</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På berghäll i äldre barrblandskog</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2447,7 +2445,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog,  naturskog</t>
+          <t>Äldre barrblandskog, naturskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2551,11 +2549,6 @@
           <t>2024-10-19</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Blåmossa mäter 50 cm</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2591,10 +2584,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120506916</v>
+        <v>120523332</v>
       </c>
       <c r="B18" t="n">
-        <v>57336</v>
+        <v>90545</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2603,39 +2596,34 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2643,13 +2631,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>339264</v>
+        <v>339216</v>
       </c>
       <c r="R18" t="n">
-        <v>6433295</v>
+        <v>6433303</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2673,12 +2661,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Växer från undersidan av barrlåga, täcker upp 110 cm längst stammen.  3 st utvecklade tickor. Bergsbrant ner till mindre kärr.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2687,6 +2680,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2712,6 +2706,127 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120506596</v>
+      </c>
+      <c r="B19" t="n">
+        <v>94704</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>339228</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6433280</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog,  naturskog</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120252553</v>
+        <v>120252645</v>
       </c>
       <c r="B4" t="n">
-        <v>57336</v>
+        <v>5189</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,20 +915,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -937,11 +937,12 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -951,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>339326</v>
+        <v>339324</v>
       </c>
       <c r="R4" t="n">
-        <v>6433296</v>
+        <v>6433300</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -991,7 +992,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spillkråkehack vid basen hos en högstubbe av tall eller gran.</t>
+          <t>5-6 mm breda gnagspår i veden samt sneda ingångshål noterades på ett relativt klent torrträd av gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,6 +1001,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1018,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120252502</v>
+        <v>120253024</v>
       </c>
       <c r="B5" t="n">
-        <v>96198</v>
+        <v>5169</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,35 +1036,32 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1070,7 +1069,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>339314</v>
+        <v>339324</v>
       </c>
       <c r="R5" t="n">
         <v>6433300</v>
@@ -1106,6 +1105,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Noterades på samma relativt klena torrträd av gran som den vågbandade barkbocken.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120253024</v>
+        <v>120252553</v>
       </c>
       <c r="B6" t="n">
-        <v>5169</v>
+        <v>57336</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,34 +1149,33 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1182,10 +1185,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>339324</v>
+        <v>339326</v>
       </c>
       <c r="R6" t="n">
-        <v>6433300</v>
+        <v>6433296</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1222,7 +1225,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Noterades på samma relativt klena torrträd av gran som den vågbandade barkbocken.</t>
+          <t>Spillkråkehack vid basen hos en högstubbe av tall eller gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,7 +1234,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1250,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120252645</v>
+        <v>120252502</v>
       </c>
       <c r="B7" t="n">
-        <v>5189</v>
+        <v>96198</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,32 +1268,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1299,7 +1304,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>339324</v>
+        <v>339314</v>
       </c>
       <c r="R7" t="n">
         <v>6433300</v>
@@ -1335,11 +1340,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>5-6 mm breda gnagspår i veden samt sneda ingångshål noterades på ett relativt klent torrträd av gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120271800</v>
+        <v>120271353</v>
       </c>
       <c r="B9" t="n">
-        <v>56292</v>
+        <v>57336</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,20 +1499,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100088</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1520,19 +1520,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1540,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>339227</v>
+        <v>339298</v>
       </c>
       <c r="R9" t="n">
-        <v>6433304</v>
+        <v>6433301</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1594,7 +1585,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1613,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120271353</v>
+        <v>120271284</v>
       </c>
       <c r="B10" t="n">
-        <v>57336</v>
+        <v>94704</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1625,31 +1615,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1692,7 +1682,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1702,7 +1692,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,6 +1701,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1729,10 +1720,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120271284</v>
+        <v>120271800</v>
       </c>
       <c r="B11" t="n">
-        <v>94704</v>
+        <v>56292</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1745,27 +1736,36 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>100088</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>339298</v>
+        <v>339227</v>
       </c>
       <c r="R11" t="n">
-        <v>6433301</v>
+        <v>6433304</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1846,10 +1846,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120506478</v>
+        <v>120506336</v>
       </c>
       <c r="B12" t="n">
-        <v>96198</v>
+        <v>84228</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1862,27 +1862,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2569</v>
+        <v>3518</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1890,10 +1893,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>339233</v>
+        <v>339237</v>
       </c>
       <c r="R12" t="n">
-        <v>6433302</v>
+        <v>6433281</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1930,7 +1933,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikt med tuvor av stor revmossa</t>
+          <t>På berghäll i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1968,10 +1971,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120506387</v>
+        <v>120506916</v>
       </c>
       <c r="B13" t="n">
-        <v>5189</v>
+        <v>57336</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1980,20 +1983,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2001,13 +2004,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2017,13 +2023,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>339233</v>
+        <v>339264</v>
       </c>
       <c r="R13" t="n">
-        <v>6433302</v>
+        <v>6433295</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2061,7 +2067,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2072,7 +2077,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog,  naturskog</t>
+          <t>Äldre barrblandskog, naturskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2214,10 +2219,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120506336</v>
+        <v>120506387</v>
       </c>
       <c r="B15" t="n">
-        <v>84228</v>
+        <v>5189</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2230,30 +2235,32 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3518</v>
+        <v>105930</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2261,10 +2268,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>339237</v>
+        <v>339233</v>
       </c>
       <c r="R15" t="n">
-        <v>6433281</v>
+        <v>6433302</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2297,11 +2304,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På berghäll i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2339,10 +2341,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120506916</v>
+        <v>120506596</v>
       </c>
       <c r="B16" t="n">
-        <v>57336</v>
+        <v>94704</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2351,39 +2353,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2391,13 +2389,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>339264</v>
+        <v>339228</v>
       </c>
       <c r="R16" t="n">
-        <v>6433295</v>
+        <v>6433280</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2435,6 +2433,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2445,7 +2444,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog, naturskog</t>
+          <t>Äldre barrblandskog,  naturskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2709,14 +2708,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120506596</v>
+        <v>120506478</v>
       </c>
       <c r="B19" t="n">
-        <v>94704</v>
+        <v>96198</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2725,28 +2724,24 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>2569</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -2757,10 +2752,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>339228</v>
+        <v>339233</v>
       </c>
       <c r="R19" t="n">
-        <v>6433280</v>
+        <v>6433302</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2793,6 +2788,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikt med tuvor av stor revmossa</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120252645</v>
+        <v>120252502</v>
       </c>
       <c r="B4" t="n">
-        <v>5189</v>
+        <v>96198</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,32 +919,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -952,7 +955,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>339324</v>
+        <v>339314</v>
       </c>
       <c r="R4" t="n">
         <v>6433300</v>
@@ -988,11 +991,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>5-6 mm breda gnagspår i veden samt sneda ingångshål noterades på ett relativt klent torrträd av gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120253024</v>
+        <v>120252645</v>
       </c>
       <c r="B5" t="n">
-        <v>5169</v>
+        <v>5189</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1034,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1109,7 +1107,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Noterades på samma relativt klena torrträd av gran som den vågbandade barkbocken.</t>
+          <t>5-6 mm breda gnagspår i veden samt sneda ingångshål noterades på ett relativt klent torrträd av gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120252553</v>
+        <v>120253024</v>
       </c>
       <c r="B6" t="n">
-        <v>57336</v>
+        <v>5169</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,33 +1147,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1185,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>339326</v>
+        <v>339324</v>
       </c>
       <c r="R6" t="n">
-        <v>6433296</v>
+        <v>6433300</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1225,7 +1224,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Spillkråkehack vid basen hos en högstubbe av tall eller gran.</t>
+          <t>Noterades på samma relativt klena torrträd av gran som den vågbandade barkbocken.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,6 +1233,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1252,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120252502</v>
+        <v>120252553</v>
       </c>
       <c r="B7" t="n">
-        <v>96198</v>
+        <v>57336</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,39 +1264,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1304,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>339314</v>
+        <v>339326</v>
       </c>
       <c r="R7" t="n">
-        <v>6433300</v>
+        <v>6433296</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1342,13 +1338,17 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Spillkråkehack vid basen hos en högstubbe av tall eller gran.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1367,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120271247</v>
+        <v>120271284</v>
       </c>
       <c r="B8" t="n">
-        <v>57336</v>
+        <v>94704</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,35 +1379,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1415,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>339227</v>
+        <v>339298</v>
       </c>
       <c r="R8" t="n">
-        <v>6433304</v>
+        <v>6433301</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1469,6 +1465,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1603,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120271284</v>
+        <v>120271247</v>
       </c>
       <c r="B10" t="n">
-        <v>94704</v>
+        <v>57336</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,31 +1612,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1647,10 +1648,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>339298</v>
+        <v>339227</v>
       </c>
       <c r="R10" t="n">
-        <v>6433301</v>
+        <v>6433304</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1701,7 +1702,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1971,10 +1971,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120506916</v>
+        <v>120506864</v>
       </c>
       <c r="B13" t="n">
-        <v>57336</v>
+        <v>57689</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,20 +1983,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -2023,13 +2023,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>339264</v>
+        <v>339229</v>
       </c>
       <c r="R13" t="n">
-        <v>6433295</v>
+        <v>6433280</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog, naturskog</t>
+          <t>Äldre barrblandskog,  naturskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2095,10 +2095,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120506864</v>
+        <v>120506387</v>
       </c>
       <c r="B14" t="n">
-        <v>57689</v>
+        <v>5189</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2111,16 +2111,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2128,16 +2128,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2147,10 +2144,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>339229</v>
+        <v>339233</v>
       </c>
       <c r="R14" t="n">
-        <v>6433280</v>
+        <v>6433302</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2191,6 +2188,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2219,10 +2217,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120506387</v>
+        <v>120506916</v>
       </c>
       <c r="B15" t="n">
-        <v>5189</v>
+        <v>57336</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2231,20 +2229,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2252,13 +2250,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2268,13 +2269,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>339233</v>
+        <v>339264</v>
       </c>
       <c r="R15" t="n">
-        <v>6433302</v>
+        <v>6433295</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2312,7 +2313,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog,  naturskog</t>
+          <t>Äldre barrblandskog, naturskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120506617</v>
+        <v>120523332</v>
       </c>
       <c r="B17" t="n">
-        <v>94704</v>
+        <v>90545</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2478,31 +2478,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2510,7 +2509,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>339229</v>
+        <v>339216</v>
       </c>
       <c r="R17" t="n">
         <v>6433303</v>
@@ -2540,12 +2539,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Växer från undersidan av barrlåga, täcker upp 110 cm längst stammen.  3 st utvecklade tickor. Bergsbrant ner till mindre kärr.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2583,10 +2587,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120523332</v>
+        <v>120506617</v>
       </c>
       <c r="B18" t="n">
-        <v>90545</v>
+        <v>94704</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2599,30 +2603,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2630,7 +2635,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>339216</v>
+        <v>339229</v>
       </c>
       <c r="R18" t="n">
         <v>6433303</v>
@@ -2660,17 +2665,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Växer från undersidan av barrlåga, täcker upp 110 cm längst stammen.  3 st utvecklade tickor. Bergsbrant ner till mindre kärr.</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2828,6 +2828,128 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120548909</v>
+      </c>
+      <c r="B20" t="n">
+        <v>95517</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>339220</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6433300</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Se gula pilar i foto.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -1849,7 +1849,7 @@
         <v>120506916</v>
       </c>
       <c r="B12" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -1864,11 +1864,6 @@
       <c r="E12" t="n">
         <v>100049</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -1849,7 +1849,7 @@
         <v>120506916</v>
       </c>
       <c r="B12" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1863,6 +1863,11 @@
       </c>
       <c r="E12" t="n">
         <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -1723,11 +1723,11 @@
         <v>120271800</v>
       </c>
       <c r="B11" t="n">
-        <v>56304</v>
+        <v>56448</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -1723,7 +1723,7 @@
         <v>120271800</v>
       </c>
       <c r="B11" t="n">
-        <v>56448</v>
+        <v>56451</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -1723,7 +1723,7 @@
         <v>120271800</v>
       </c>
       <c r="B11" t="n">
-        <v>56451</v>
+        <v>56457</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>120506916</v>
       </c>
       <c r="B12" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -1849,7 +1849,7 @@
         <v>120506916</v>
       </c>
       <c r="B12" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -1849,7 +1849,7 @@
         <v>120506916</v>
       </c>
       <c r="B12" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -3332,10 +3332,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124628273</v>
+        <v>124628199</v>
       </c>
       <c r="B24" t="n">
-        <v>95345</v>
+        <v>5196</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3348,27 +3348,32 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2810</v>
+        <v>105930</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3411,7 +3416,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3421,7 +3426,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3449,10 +3454,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124628199</v>
+        <v>124628273</v>
       </c>
       <c r="B25" t="n">
-        <v>5196</v>
+        <v>95345</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3465,32 +3470,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>105930</v>
+        <v>2810</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3569,6 +3569,516 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>124794443</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80763</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Torraka, Vg</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>339301</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6433307</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>124794445</v>
+      </c>
+      <c r="B27" t="n">
+        <v>74840</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Klen gran, Vg</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>339238</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6433294</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>124794442</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80763</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Torraka, Vg</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>339321</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6433292</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>124794444</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80763</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Torraka nära myr, Vg</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>339266</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6433304</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>124794446</v>
+      </c>
+      <c r="B30" t="n">
+        <v>74893</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>308</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Torraka, Vg</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>339228</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6433304</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -3332,10 +3332,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124628199</v>
+        <v>124628273</v>
       </c>
       <c r="B24" t="n">
-        <v>5196</v>
+        <v>95345</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3348,32 +3348,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>105930</v>
+        <v>2810</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3416,7 +3411,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3426,7 +3421,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3454,10 +3449,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124628273</v>
+        <v>124628199</v>
       </c>
       <c r="B25" t="n">
-        <v>95345</v>
+        <v>5196</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3470,27 +3465,32 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2810</v>
+        <v>105930</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3571,7 +3571,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124794443</v>
+        <v>124794444</v>
       </c>
       <c r="B26" t="n">
         <v>80763</v>
@@ -3607,14 +3607,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Torraka, Vg</t>
+          <t>Torraka nära myr, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>339301</v>
+        <v>339266</v>
       </c>
       <c r="R26" t="n">
-        <v>6433307</v>
+        <v>6433304</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3673,10 +3673,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124794445</v>
+        <v>124794442</v>
       </c>
       <c r="B27" t="n">
-        <v>74840</v>
+        <v>80763</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3685,38 +3685,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
+        <v>1049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Klen gran, Vg</t>
+          <t>Torraka, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>339238</v>
+        <v>339321</v>
       </c>
       <c r="R27" t="n">
-        <v>6433294</v>
+        <v>6433292</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3775,10 +3775,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124794442</v>
+        <v>124794445</v>
       </c>
       <c r="B28" t="n">
-        <v>80763</v>
+        <v>74840</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3787,38 +3787,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>6426</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Torraka, Vg</t>
+          <t>Klen gran, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>339321</v>
+        <v>339238</v>
       </c>
       <c r="R28" t="n">
-        <v>6433292</v>
+        <v>6433294</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3877,7 +3877,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124794444</v>
+        <v>124794443</v>
       </c>
       <c r="B29" t="n">
         <v>80763</v>
@@ -3913,14 +3913,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Torraka nära myr, Vg</t>
+          <t>Torraka, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>339266</v>
+        <v>339301</v>
       </c>
       <c r="R29" t="n">
-        <v>6433304</v>
+        <v>6433307</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -3332,10 +3332,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124628273</v>
+        <v>124628199</v>
       </c>
       <c r="B24" t="n">
-        <v>95345</v>
+        <v>5196</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3348,27 +3348,32 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2810</v>
+        <v>105930</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3411,7 +3416,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3421,7 +3426,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3449,10 +3454,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124628199</v>
+        <v>124628273</v>
       </c>
       <c r="B25" t="n">
-        <v>5196</v>
+        <v>95345</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3465,32 +3470,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>105930</v>
+        <v>2810</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3571,10 +3571,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124794444</v>
+        <v>124794445</v>
       </c>
       <c r="B26" t="n">
-        <v>80763</v>
+        <v>74840</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3583,38 +3583,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1049</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Torraka nära myr, Vg</t>
+          <t>Klen gran, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>339266</v>
+        <v>339238</v>
       </c>
       <c r="R26" t="n">
-        <v>6433304</v>
+        <v>6433294</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3673,7 +3673,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124794442</v>
+        <v>124794444</v>
       </c>
       <c r="B27" t="n">
         <v>80763</v>
@@ -3709,14 +3709,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Torraka, Vg</t>
+          <t>Torraka nära myr, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>339321</v>
+        <v>339266</v>
       </c>
       <c r="R27" t="n">
-        <v>6433292</v>
+        <v>6433304</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3775,10 +3775,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124794445</v>
+        <v>124794443</v>
       </c>
       <c r="B28" t="n">
-        <v>74840</v>
+        <v>80763</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3787,38 +3787,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6426</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Klen gran, Vg</t>
+          <t>Torraka, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>339238</v>
+        <v>339301</v>
       </c>
       <c r="R28" t="n">
-        <v>6433294</v>
+        <v>6433307</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3877,7 +3877,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124794443</v>
+        <v>124794442</v>
       </c>
       <c r="B29" t="n">
         <v>80763</v>
@@ -3917,10 +3917,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>339301</v>
+        <v>339321</v>
       </c>
       <c r="R29" t="n">
-        <v>6433307</v>
+        <v>6433292</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -3571,10 +3571,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124794445</v>
+        <v>124794444</v>
       </c>
       <c r="B26" t="n">
-        <v>74840</v>
+        <v>80763</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3583,38 +3583,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>1049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Klen gran, Vg</t>
+          <t>Torraka nära myr, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>339238</v>
+        <v>339266</v>
       </c>
       <c r="R26" t="n">
-        <v>6433294</v>
+        <v>6433304</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3673,10 +3673,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124794444</v>
+        <v>124794445</v>
       </c>
       <c r="B27" t="n">
-        <v>80763</v>
+        <v>74840</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3685,38 +3685,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Torraka nära myr, Vg</t>
+          <t>Klen gran, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>339266</v>
+        <v>339238</v>
       </c>
       <c r="R27" t="n">
-        <v>6433304</v>
+        <v>6433294</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3775,7 +3775,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124794443</v>
+        <v>124794442</v>
       </c>
       <c r="B28" t="n">
         <v>80763</v>
@@ -3815,10 +3815,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>339301</v>
+        <v>339321</v>
       </c>
       <c r="R28" t="n">
-        <v>6433307</v>
+        <v>6433292</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3877,10 +3877,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124794442</v>
+        <v>124794446</v>
       </c>
       <c r="B29" t="n">
-        <v>80763</v>
+        <v>74893</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3893,21 +3893,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1049</v>
+        <v>308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3917,10 +3917,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>339321</v>
+        <v>339228</v>
       </c>
       <c r="R29" t="n">
-        <v>6433292</v>
+        <v>6433304</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3979,10 +3979,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124794446</v>
+        <v>124794443</v>
       </c>
       <c r="B30" t="n">
-        <v>74893</v>
+        <v>80763</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3995,21 +3995,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>308</v>
+        <v>1049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>339228</v>
+        <v>339301</v>
       </c>
       <c r="R30" t="n">
-        <v>6433304</v>
+        <v>6433307</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -3332,10 +3332,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124628199</v>
+        <v>124628273</v>
       </c>
       <c r="B24" t="n">
-        <v>5196</v>
+        <v>95345</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3348,32 +3348,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>105930</v>
+        <v>2810</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3416,7 +3411,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3426,7 +3421,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3454,10 +3449,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124628273</v>
+        <v>124628199</v>
       </c>
       <c r="B25" t="n">
-        <v>95345</v>
+        <v>5196</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3470,27 +3465,32 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2810</v>
+        <v>105930</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3673,10 +3673,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124794445</v>
+        <v>124794442</v>
       </c>
       <c r="B27" t="n">
-        <v>74840</v>
+        <v>80763</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3685,38 +3685,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
+        <v>1049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Klen gran, Vg</t>
+          <t>Torraka, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>339238</v>
+        <v>339321</v>
       </c>
       <c r="R27" t="n">
-        <v>6433294</v>
+        <v>6433292</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3775,7 +3775,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124794442</v>
+        <v>124794443</v>
       </c>
       <c r="B28" t="n">
         <v>80763</v>
@@ -3815,10 +3815,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>339321</v>
+        <v>339301</v>
       </c>
       <c r="R28" t="n">
-        <v>6433292</v>
+        <v>6433307</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3877,10 +3877,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124794446</v>
+        <v>124794445</v>
       </c>
       <c r="B29" t="n">
-        <v>74893</v>
+        <v>74840</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3889,38 +3889,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>308</v>
+        <v>6426</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Torraka, Vg</t>
+          <t>Klen gran, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>339228</v>
+        <v>339238</v>
       </c>
       <c r="R29" t="n">
-        <v>6433304</v>
+        <v>6433294</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3979,10 +3979,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124794443</v>
+        <v>124794446</v>
       </c>
       <c r="B30" t="n">
-        <v>80763</v>
+        <v>74893</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3995,21 +3995,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1049</v>
+        <v>308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>339301</v>
+        <v>339228</v>
       </c>
       <c r="R30" t="n">
-        <v>6433307</v>
+        <v>6433304</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -3571,10 +3571,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124794444</v>
+        <v>124794445</v>
       </c>
       <c r="B26" t="n">
-        <v>80763</v>
+        <v>74840</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3583,38 +3583,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1049</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Torraka nära myr, Vg</t>
+          <t>Klen gran, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>339266</v>
+        <v>339238</v>
       </c>
       <c r="R26" t="n">
-        <v>6433304</v>
+        <v>6433294</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3673,7 +3673,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124794442</v>
+        <v>124794443</v>
       </c>
       <c r="B27" t="n">
         <v>80763</v>
@@ -3713,10 +3713,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>339321</v>
+        <v>339301</v>
       </c>
       <c r="R27" t="n">
-        <v>6433292</v>
+        <v>6433307</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3775,10 +3775,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124794443</v>
+        <v>124794446</v>
       </c>
       <c r="B28" t="n">
-        <v>80763</v>
+        <v>74893</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3791,21 +3791,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3815,10 +3815,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>339301</v>
+        <v>339228</v>
       </c>
       <c r="R28" t="n">
-        <v>6433307</v>
+        <v>6433304</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3877,10 +3877,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124794445</v>
+        <v>124794442</v>
       </c>
       <c r="B29" t="n">
-        <v>74840</v>
+        <v>80763</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3889,38 +3889,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6426</v>
+        <v>1049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Klen gran, Vg</t>
+          <t>Torraka, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>339238</v>
+        <v>339321</v>
       </c>
       <c r="R29" t="n">
-        <v>6433294</v>
+        <v>6433292</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3979,10 +3979,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124794446</v>
+        <v>124794444</v>
       </c>
       <c r="B30" t="n">
-        <v>74893</v>
+        <v>80763</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3995,31 +3995,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>308</v>
+        <v>1049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Torraka, Vg</t>
+          <t>Torraka nära myr, Vg</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>339228</v>
+        <v>339266</v>
       </c>
       <c r="R30" t="n">
         <v>6433304</v>

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -3571,10 +3571,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124794445</v>
+        <v>124794443</v>
       </c>
       <c r="B26" t="n">
-        <v>74840</v>
+        <v>80763</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3583,38 +3583,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>1049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Klen gran, Vg</t>
+          <t>Torraka, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>339238</v>
+        <v>339301</v>
       </c>
       <c r="R26" t="n">
-        <v>6433294</v>
+        <v>6433307</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3673,7 +3673,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124794443</v>
+        <v>124794444</v>
       </c>
       <c r="B27" t="n">
         <v>80763</v>
@@ -3709,14 +3709,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Torraka, Vg</t>
+          <t>Torraka nära myr, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>339301</v>
+        <v>339266</v>
       </c>
       <c r="R27" t="n">
-        <v>6433307</v>
+        <v>6433304</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3775,10 +3775,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124794446</v>
+        <v>124794442</v>
       </c>
       <c r="B28" t="n">
-        <v>74893</v>
+        <v>80763</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3791,21 +3791,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>308</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3815,10 +3815,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>339228</v>
+        <v>339321</v>
       </c>
       <c r="R28" t="n">
-        <v>6433304</v>
+        <v>6433292</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3877,10 +3877,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124794442</v>
+        <v>124794445</v>
       </c>
       <c r="B29" t="n">
-        <v>80763</v>
+        <v>74840</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3889,38 +3889,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1049</v>
+        <v>6426</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Torraka, Vg</t>
+          <t>Klen gran, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>339321</v>
+        <v>339238</v>
       </c>
       <c r="R29" t="n">
-        <v>6433292</v>
+        <v>6433294</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3979,10 +3979,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124794444</v>
+        <v>124794446</v>
       </c>
       <c r="B30" t="n">
-        <v>80763</v>
+        <v>74893</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3995,31 +3995,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1049</v>
+        <v>308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Torraka nära myr, Vg</t>
+          <t>Torraka, Vg</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>339266</v>
+        <v>339228</v>
       </c>
       <c r="R30" t="n">
         <v>6433304</v>

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -3332,10 +3332,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124628273</v>
+        <v>124628199</v>
       </c>
       <c r="B24" t="n">
-        <v>95345</v>
+        <v>5196</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3348,27 +3348,32 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2810</v>
+        <v>105930</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3411,7 +3416,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3421,7 +3426,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3449,10 +3454,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124628199</v>
+        <v>124628273</v>
       </c>
       <c r="B25" t="n">
-        <v>5196</v>
+        <v>95345</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3465,32 +3470,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>105930</v>
+        <v>2810</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3571,10 +3571,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124794443</v>
+        <v>124794445</v>
       </c>
       <c r="B26" t="n">
-        <v>80763</v>
+        <v>74840</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3583,38 +3583,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1049</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Torraka, Vg</t>
+          <t>Klen gran, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>339301</v>
+        <v>339238</v>
       </c>
       <c r="R26" t="n">
-        <v>6433307</v>
+        <v>6433294</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3673,10 +3673,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124794444</v>
+        <v>124794446</v>
       </c>
       <c r="B27" t="n">
-        <v>80763</v>
+        <v>74893</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3689,31 +3689,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Torraka nära myr, Vg</t>
+          <t>Torraka, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>339266</v>
+        <v>339228</v>
       </c>
       <c r="R27" t="n">
         <v>6433304</v>
@@ -3877,10 +3877,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124794445</v>
+        <v>124794444</v>
       </c>
       <c r="B29" t="n">
-        <v>74840</v>
+        <v>80763</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3889,38 +3889,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6426</v>
+        <v>1049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Klen gran, Vg</t>
+          <t>Torraka nära myr, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>339238</v>
+        <v>339266</v>
       </c>
       <c r="R29" t="n">
-        <v>6433294</v>
+        <v>6433304</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3979,10 +3979,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124794446</v>
+        <v>124794443</v>
       </c>
       <c r="B30" t="n">
-        <v>74893</v>
+        <v>80763</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3995,21 +3995,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>308</v>
+        <v>1049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>339228</v>
+        <v>339301</v>
       </c>
       <c r="R30" t="n">
-        <v>6433304</v>
+        <v>6433307</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -3571,10 +3571,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124794445</v>
+        <v>124794446</v>
       </c>
       <c r="B26" t="n">
-        <v>74840</v>
+        <v>74893</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3583,38 +3583,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Klen gran, Vg</t>
+          <t>Torraka, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>339238</v>
+        <v>339228</v>
       </c>
       <c r="R26" t="n">
-        <v>6433294</v>
+        <v>6433304</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3673,10 +3673,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124794446</v>
+        <v>124794442</v>
       </c>
       <c r="B27" t="n">
-        <v>74893</v>
+        <v>80763</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3689,21 +3689,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>308</v>
+        <v>1049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3713,10 +3713,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>339228</v>
+        <v>339321</v>
       </c>
       <c r="R27" t="n">
-        <v>6433304</v>
+        <v>6433292</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3775,10 +3775,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124794442</v>
+        <v>124794445</v>
       </c>
       <c r="B28" t="n">
-        <v>80763</v>
+        <v>74840</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3787,38 +3787,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>6426</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Torraka, Vg</t>
+          <t>Klen gran, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>339321</v>
+        <v>339238</v>
       </c>
       <c r="R28" t="n">
-        <v>6433292</v>
+        <v>6433294</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -3332,10 +3332,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124628199</v>
+        <v>124628273</v>
       </c>
       <c r="B24" t="n">
-        <v>5196</v>
+        <v>95345</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3348,32 +3348,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>105930</v>
+        <v>2810</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3416,7 +3411,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3426,7 +3421,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3454,10 +3449,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124628273</v>
+        <v>124628199</v>
       </c>
       <c r="B25" t="n">
-        <v>95345</v>
+        <v>5196</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3470,27 +3465,32 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2810</v>
+        <v>105930</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3571,10 +3571,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124794446</v>
+        <v>124794444</v>
       </c>
       <c r="B26" t="n">
-        <v>74893</v>
+        <v>80763</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3587,31 +3587,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>308</v>
+        <v>1049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Torraka, Vg</t>
+          <t>Torraka nära myr, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>339228</v>
+        <v>339266</v>
       </c>
       <c r="R26" t="n">
         <v>6433304</v>
@@ -3673,10 +3673,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124794442</v>
+        <v>124794446</v>
       </c>
       <c r="B27" t="n">
-        <v>80763</v>
+        <v>74893</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3689,21 +3689,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3713,10 +3713,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>339321</v>
+        <v>339228</v>
       </c>
       <c r="R27" t="n">
-        <v>6433292</v>
+        <v>6433304</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3775,10 +3775,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124794445</v>
+        <v>124794443</v>
       </c>
       <c r="B28" t="n">
-        <v>74840</v>
+        <v>80763</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3787,38 +3787,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6426</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Klen gran, Vg</t>
+          <t>Torraka, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>339238</v>
+        <v>339301</v>
       </c>
       <c r="R28" t="n">
-        <v>6433294</v>
+        <v>6433307</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3877,10 +3877,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124794444</v>
+        <v>124794445</v>
       </c>
       <c r="B29" t="n">
-        <v>80763</v>
+        <v>74840</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3889,38 +3889,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1049</v>
+        <v>6426</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Torraka nära myr, Vg</t>
+          <t>Klen gran, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>339266</v>
+        <v>339238</v>
       </c>
       <c r="R29" t="n">
-        <v>6433304</v>
+        <v>6433294</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3979,7 +3979,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124794443</v>
+        <v>124794442</v>
       </c>
       <c r="B30" t="n">
         <v>80763</v>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>339301</v>
+        <v>339321</v>
       </c>
       <c r="R30" t="n">
-        <v>6433307</v>
+        <v>6433292</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -3571,10 +3571,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124794444</v>
+        <v>124794446</v>
       </c>
       <c r="B26" t="n">
-        <v>80763</v>
+        <v>74893</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3587,31 +3587,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1049</v>
+        <v>308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Torraka nära myr, Vg</t>
+          <t>Torraka, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>339266</v>
+        <v>339228</v>
       </c>
       <c r="R26" t="n">
         <v>6433304</v>
@@ -3673,10 +3673,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124794446</v>
+        <v>124794444</v>
       </c>
       <c r="B27" t="n">
-        <v>74893</v>
+        <v>80763</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3689,31 +3689,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>308</v>
+        <v>1049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Torraka, Vg</t>
+          <t>Torraka nära myr, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>339228</v>
+        <v>339266</v>
       </c>
       <c r="R27" t="n">
         <v>6433304</v>

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -3332,10 +3332,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124628273</v>
+        <v>124628199</v>
       </c>
       <c r="B24" t="n">
-        <v>95345</v>
+        <v>5196</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3348,27 +3348,32 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2810</v>
+        <v>105930</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3411,7 +3416,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3421,7 +3426,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3449,10 +3454,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124628199</v>
+        <v>124628273</v>
       </c>
       <c r="B25" t="n">
-        <v>5196</v>
+        <v>95513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3465,32 +3470,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>105930</v>
+        <v>2810</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3571,10 +3571,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124794446</v>
+        <v>124794443</v>
       </c>
       <c r="B26" t="n">
-        <v>74893</v>
+        <v>80900</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3587,21 +3587,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>308</v>
+        <v>1049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3611,10 +3611,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>339228</v>
+        <v>339301</v>
       </c>
       <c r="R26" t="n">
-        <v>6433304</v>
+        <v>6433307</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3673,10 +3673,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124794444</v>
+        <v>124794445</v>
       </c>
       <c r="B27" t="n">
-        <v>80763</v>
+        <v>74964</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3685,38 +3685,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Torraka nära myr, Vg</t>
+          <t>Klen gran, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>339266</v>
+        <v>339238</v>
       </c>
       <c r="R27" t="n">
-        <v>6433304</v>
+        <v>6433294</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3775,10 +3775,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124794443</v>
+        <v>124794446</v>
       </c>
       <c r="B28" t="n">
-        <v>80763</v>
+        <v>75017</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3791,21 +3791,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3815,10 +3815,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>339301</v>
+        <v>339228</v>
       </c>
       <c r="R28" t="n">
-        <v>6433307</v>
+        <v>6433304</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3877,10 +3877,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124794445</v>
+        <v>124794442</v>
       </c>
       <c r="B29" t="n">
-        <v>74840</v>
+        <v>80900</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3889,38 +3889,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6426</v>
+        <v>1049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Klen gran, Vg</t>
+          <t>Torraka, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>339238</v>
+        <v>339321</v>
       </c>
       <c r="R29" t="n">
-        <v>6433294</v>
+        <v>6433292</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3979,10 +3979,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124794442</v>
+        <v>124794444</v>
       </c>
       <c r="B30" t="n">
-        <v>80763</v>
+        <v>80900</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4015,14 +4015,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Torraka, Vg</t>
+          <t>Torraka nära myr, Vg</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>339321</v>
+        <v>339266</v>
       </c>
       <c r="R30" t="n">
-        <v>6433292</v>
+        <v>6433304</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 39593-2024 artfynd.xlsx
+++ b/artfynd/A 39593-2024 artfynd.xlsx
@@ -3775,10 +3775,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124794446</v>
+        <v>124794444</v>
       </c>
       <c r="B28" t="n">
-        <v>75017</v>
+        <v>80900</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3791,31 +3791,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>308</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Torraka, Vg</t>
+          <t>Torraka nära myr, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>339228</v>
+        <v>339266</v>
       </c>
       <c r="R28" t="n">
         <v>6433304</v>
@@ -3979,10 +3979,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124794444</v>
+        <v>124794446</v>
       </c>
       <c r="B30" t="n">
-        <v>80900</v>
+        <v>75017</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3995,31 +3995,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1049</v>
+        <v>308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Torraka nära myr, Vg</t>
+          <t>Torraka, Vg</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>339266</v>
+        <v>339228</v>
       </c>
       <c r="R30" t="n">
         <v>6433304</v>
